--- a/data/base/Backlog_3.xlsx
+++ b/data/base/Backlog_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9B4DF0-BB71-47B4-BB9C-5DA1FD5DFC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81B090C-B4A4-4E7A-B0EC-A6CE5DD2DE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="31">
   <si>
     <t>Backlog</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t>Maria Eduarda</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -236,51 +239,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,52 +600,52 @@
   <dimension ref="A1:K58"/>
   <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.5703125" style="1"/>
+    <col min="1" max="1" width="10.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.5703125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -652,7 +654,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C2" s="12">
         <v>2026</v>
@@ -660,19 +662,19 @@
       <c r="D2" s="12">
         <v>3</v>
       </c>
-      <c r="E2" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F2" s="13">
+      <c r="E2" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F2" s="4">
         <v>46052</v>
       </c>
       <c r="G2" s="12">
-        <v>3974</v>
-      </c>
-      <c r="H2" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I2" s="13">
+        <v>8852</v>
+      </c>
+      <c r="H2" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I2" s="4">
         <v>46048</v>
       </c>
       <c r="J2" s="12" t="s">
@@ -687,7 +689,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="12">
         <v>2026</v>
@@ -695,19 +697,19 @@
       <c r="D3" s="12">
         <v>3</v>
       </c>
-      <c r="E3" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F3" s="13">
+      <c r="E3" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F3" s="4">
         <v>46052</v>
       </c>
       <c r="G3" s="12">
-        <v>5259</v>
-      </c>
-      <c r="H3" s="14">
-        <v>45962</v>
-      </c>
-      <c r="I3" s="13">
+        <v>7400</v>
+      </c>
+      <c r="H3" s="5">
+        <v>45931</v>
+      </c>
+      <c r="I3" s="4">
         <v>46048</v>
       </c>
       <c r="J3" s="12" t="s">
@@ -722,7 +724,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C4" s="12">
         <v>2026</v>
@@ -730,23 +732,23 @@
       <c r="D4" s="12">
         <v>3</v>
       </c>
-      <c r="E4" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F4" s="13">
+      <c r="E4" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F4" s="4">
         <v>46052</v>
       </c>
       <c r="G4" s="12">
-        <v>6015</v>
-      </c>
-      <c r="H4" s="14">
-        <v>45962</v>
-      </c>
-      <c r="I4" s="13">
+        <v>8861</v>
+      </c>
+      <c r="H4" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I4" s="4">
         <v>46048</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>11</v>
@@ -757,7 +759,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5" s="12">
         <v>2026</v>
@@ -765,19 +767,19 @@
       <c r="D5" s="12">
         <v>3</v>
       </c>
-      <c r="E5" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F5" s="13">
+      <c r="E5" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F5" s="4">
         <v>46052</v>
       </c>
       <c r="G5" s="12">
-        <v>7400</v>
-      </c>
-      <c r="H5" s="14">
-        <v>45931</v>
-      </c>
-      <c r="I5" s="13">
+        <v>8902</v>
+      </c>
+      <c r="H5" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I5" s="4">
         <v>46048</v>
       </c>
       <c r="J5" s="12" t="s">
@@ -792,7 +794,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" s="12">
         <v>2026</v>
@@ -800,19 +802,19 @@
       <c r="D6" s="12">
         <v>3</v>
       </c>
-      <c r="E6" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F6" s="13">
+      <c r="E6" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F6" s="4">
         <v>46052</v>
       </c>
       <c r="G6" s="12">
-        <v>8372</v>
-      </c>
-      <c r="H6" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I6" s="13">
+        <v>9136</v>
+      </c>
+      <c r="H6" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I6" s="4">
         <v>46048</v>
       </c>
       <c r="J6" s="12" t="s">
@@ -827,7 +829,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="12">
         <v>2026</v>
@@ -835,23 +837,23 @@
       <c r="D7" s="12">
         <v>3</v>
       </c>
-      <c r="E7" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F7" s="13">
+      <c r="E7" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F7" s="4">
         <v>46052</v>
       </c>
       <c r="G7" s="12">
-        <v>8455</v>
-      </c>
-      <c r="H7" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I7" s="13">
+        <v>9191</v>
+      </c>
+      <c r="H7" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I7" s="4">
         <v>46048</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>11</v>
@@ -862,7 +864,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" s="12">
         <v>2026</v>
@@ -870,23 +872,23 @@
       <c r="D8" s="12">
         <v>3</v>
       </c>
-      <c r="E8" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F8" s="13">
+      <c r="E8" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F8" s="4">
         <v>46052</v>
       </c>
       <c r="G8" s="12">
-        <v>8571</v>
-      </c>
-      <c r="H8" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I8" s="13">
+        <v>9202</v>
+      </c>
+      <c r="H8" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I8" s="4">
         <v>46048</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K8" s="12" t="s">
         <v>11</v>
@@ -897,7 +899,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="12">
         <v>2026</v>
@@ -905,19 +907,19 @@
       <c r="D9" s="12">
         <v>3</v>
       </c>
-      <c r="E9" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F9" s="13">
+      <c r="E9" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F9" s="4">
         <v>46052</v>
       </c>
       <c r="G9" s="12">
-        <v>8852</v>
-      </c>
-      <c r="H9" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I9" s="13">
+        <v>9411</v>
+      </c>
+      <c r="H9" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I9" s="4">
         <v>46048</v>
       </c>
       <c r="J9" s="12" t="s">
@@ -932,7 +934,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C10" s="12">
         <v>2026</v>
@@ -940,23 +942,23 @@
       <c r="D10" s="12">
         <v>3</v>
       </c>
-      <c r="E10" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F10" s="13">
+      <c r="E10" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F10" s="4">
         <v>46052</v>
       </c>
       <c r="G10" s="12">
-        <v>8861</v>
-      </c>
-      <c r="H10" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I10" s="13">
+        <v>3974</v>
+      </c>
+      <c r="H10" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I10" s="4">
         <v>46048</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>11</v>
@@ -967,7 +969,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C11" s="12">
         <v>2026</v>
@@ -975,23 +977,23 @@
       <c r="D11" s="12">
         <v>3</v>
       </c>
-      <c r="E11" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F11" s="13">
+      <c r="E11" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F11" s="4">
         <v>46052</v>
       </c>
       <c r="G11" s="12">
-        <v>8902</v>
-      </c>
-      <c r="H11" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I11" s="13">
+        <v>9382</v>
+      </c>
+      <c r="H11" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I11" s="4">
         <v>46048</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K11" s="12" t="s">
         <v>11</v>
@@ -1002,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C12" s="12">
         <v>2026</v>
@@ -1010,23 +1012,23 @@
       <c r="D12" s="12">
         <v>3</v>
       </c>
-      <c r="E12" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F12" s="13">
+      <c r="E12" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F12" s="4">
         <v>46052</v>
       </c>
       <c r="G12" s="12">
-        <v>8921</v>
-      </c>
-      <c r="H12" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I12" s="13">
+        <v>8997</v>
+      </c>
+      <c r="H12" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I12" s="4">
         <v>46048</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K12" s="12" t="s">
         <v>11</v>
@@ -1037,7 +1039,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C13" s="12">
         <v>2026</v>
@@ -1045,23 +1047,23 @@
       <c r="D13" s="12">
         <v>3</v>
       </c>
-      <c r="E13" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F13" s="13">
+      <c r="E13" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F13" s="4">
         <v>46052</v>
       </c>
       <c r="G13" s="12">
-        <v>8997</v>
-      </c>
-      <c r="H13" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I13" s="13">
+        <v>8571</v>
+      </c>
+      <c r="H13" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I13" s="4">
         <v>46048</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K13" s="12" t="s">
         <v>11</v>
@@ -1072,7 +1074,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C14" s="12">
         <v>2026</v>
@@ -1080,23 +1082,23 @@
       <c r="D14" s="12">
         <v>3</v>
       </c>
-      <c r="E14" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F14" s="13">
+      <c r="E14" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F14" s="4">
         <v>46052</v>
       </c>
       <c r="G14" s="12">
-        <v>9079</v>
-      </c>
-      <c r="H14" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I14" s="13">
+        <v>9260</v>
+      </c>
+      <c r="H14" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I14" s="4">
         <v>46048</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K14" s="12" t="s">
         <v>11</v>
@@ -1107,7 +1109,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C15" s="12">
         <v>2026</v>
@@ -1115,19 +1117,19 @@
       <c r="D15" s="12">
         <v>3</v>
       </c>
-      <c r="E15" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F15" s="13">
+      <c r="E15" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F15" s="4">
         <v>46052</v>
       </c>
       <c r="G15" s="12">
-        <v>9136</v>
-      </c>
-      <c r="H15" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I15" s="13">
+        <v>9273</v>
+      </c>
+      <c r="H15" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I15" s="4">
         <v>46048</v>
       </c>
       <c r="J15" s="12" t="s">
@@ -1142,7 +1144,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C16" s="12">
         <v>2026</v>
@@ -1150,23 +1152,23 @@
       <c r="D16" s="12">
         <v>3</v>
       </c>
-      <c r="E16" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F16" s="13">
+      <c r="E16" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F16" s="4">
         <v>46052</v>
       </c>
       <c r="G16" s="12">
-        <v>9191</v>
-      </c>
-      <c r="H16" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I16" s="13">
+        <v>8372</v>
+      </c>
+      <c r="H16" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I16" s="4">
         <v>46048</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>11</v>
@@ -1177,7 +1179,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C17" s="12">
         <v>2026</v>
@@ -1185,19 +1187,19 @@
       <c r="D17" s="12">
         <v>3</v>
       </c>
-      <c r="E17" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F17" s="13">
+      <c r="E17" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F17" s="4">
         <v>46052</v>
       </c>
       <c r="G17" s="12">
-        <v>9202</v>
-      </c>
-      <c r="H17" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I17" s="13">
+        <v>9211</v>
+      </c>
+      <c r="H17" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I17" s="4">
         <v>46048</v>
       </c>
       <c r="J17" s="12" t="s">
@@ -1212,7 +1214,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C18" s="12">
         <v>2026</v>
@@ -1220,23 +1222,23 @@
       <c r="D18" s="12">
         <v>3</v>
       </c>
-      <c r="E18" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F18" s="13">
+      <c r="E18" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F18" s="4">
         <v>46052</v>
       </c>
       <c r="G18" s="12">
-        <v>9211</v>
-      </c>
-      <c r="H18" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I18" s="13">
+        <v>5259</v>
+      </c>
+      <c r="H18" s="5">
+        <v>45962</v>
+      </c>
+      <c r="I18" s="4">
         <v>46048</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K18" s="12" t="s">
         <v>11</v>
@@ -1247,7 +1249,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C19" s="12">
         <v>2026</v>
@@ -1255,23 +1257,23 @@
       <c r="D19" s="12">
         <v>3</v>
       </c>
-      <c r="E19" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F19" s="13">
+      <c r="E19" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F19" s="4">
         <v>46052</v>
       </c>
       <c r="G19" s="12">
-        <v>9260</v>
-      </c>
-      <c r="H19" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I19" s="13">
+        <v>6015</v>
+      </c>
+      <c r="H19" s="5">
+        <v>45962</v>
+      </c>
+      <c r="I19" s="4">
         <v>46048</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K19" s="12" t="s">
         <v>11</v>
@@ -1282,7 +1284,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C20" s="12">
         <v>2026</v>
@@ -1290,23 +1292,23 @@
       <c r="D20" s="12">
         <v>3</v>
       </c>
-      <c r="E20" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F20" s="13">
+      <c r="E20" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F20" s="4">
         <v>46052</v>
       </c>
       <c r="G20" s="12">
-        <v>9273</v>
-      </c>
-      <c r="H20" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I20" s="13">
+        <v>9079</v>
+      </c>
+      <c r="H20" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I20" s="4">
         <v>46048</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K20" s="12" t="s">
         <v>11</v>
@@ -1325,23 +1327,23 @@
       <c r="D21" s="12">
         <v>3</v>
       </c>
-      <c r="E21" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F21" s="13">
+      <c r="E21" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F21" s="4">
         <v>46052</v>
       </c>
       <c r="G21" s="12">
-        <v>9367</v>
-      </c>
-      <c r="H21" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I21" s="13">
+        <v>8455</v>
+      </c>
+      <c r="H21" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I21" s="4">
         <v>46048</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K21" s="12" t="s">
         <v>11</v>
@@ -1352,7 +1354,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C22" s="12">
         <v>2026</v>
@@ -1360,23 +1362,23 @@
       <c r="D22" s="12">
         <v>3</v>
       </c>
-      <c r="E22" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F22" s="13">
+      <c r="E22" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F22" s="4">
         <v>46052</v>
       </c>
       <c r="G22" s="12">
-        <v>9382</v>
-      </c>
-      <c r="H22" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I22" s="13">
+        <v>8921</v>
+      </c>
+      <c r="H22" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I22" s="4">
         <v>46048</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K22" s="12" t="s">
         <v>11</v>
@@ -1387,7 +1389,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C23" s="12">
         <v>2026</v>
@@ -1395,241 +1397,245 @@
       <c r="D23" s="12">
         <v>3</v>
       </c>
-      <c r="E23" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F23" s="13">
+      <c r="E23" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F23" s="4">
         <v>46052</v>
       </c>
       <c r="G23" s="12">
-        <v>9411</v>
-      </c>
-      <c r="H23" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I23" s="13">
+        <v>9367</v>
+      </c>
+      <c r="H23" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I23" s="4">
         <v>46048</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K23" s="12" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="6"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="6"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="8"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="6"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="8"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="6"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="8"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="6"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="8"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="6"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="8"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="6"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="8"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="6"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="8"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="6"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="8"/>
     </row>
     <row r="33" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="6"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="8"/>
     </row>
     <row r="34" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="E34" s="7"/>
-      <c r="F34" s="5"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="3"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="9"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="16"/>
     </row>
     <row r="35" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D35" s="3"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="5"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="3"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="9"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="16"/>
     </row>
     <row r="36" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D36" s="3"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="5"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="3"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="9"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="16"/>
     </row>
     <row r="37" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D37" s="3"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="3"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="16"/>
     </row>
     <row r="38" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D38" s="3"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="H38" s="2"/>
-      <c r="J38" s="3"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="H38" s="15"/>
+      <c r="J38" s="16"/>
     </row>
     <row r="39" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D39" s="3"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="6"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="8"/>
     </row>
     <row r="40" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D40" s="3"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="6"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="8"/>
     </row>
     <row r="41" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D41" s="3"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="6"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="8"/>
     </row>
     <row r="42" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D42" s="3"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="6"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="8"/>
     </row>
     <row r="43" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D43" s="3"/>
-      <c r="F43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="6"/>
+      <c r="D43" s="16"/>
+      <c r="F43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="8"/>
     </row>
     <row r="44" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D44" s="3"/>
-      <c r="F44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="6"/>
+      <c r="D44" s="16"/>
+      <c r="F44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="8"/>
     </row>
     <row r="45" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D45" s="3"/>
-      <c r="F45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="6"/>
+      <c r="D45" s="16"/>
+      <c r="F45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="8"/>
     </row>
     <row r="46" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D46" s="3"/>
-      <c r="F46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="6"/>
+      <c r="D46" s="16"/>
+      <c r="F46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="8"/>
     </row>
     <row r="47" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="F47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="6"/>
+      <c r="F47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="8"/>
     </row>
     <row r="48" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="F48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="6"/>
+      <c r="F48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="8"/>
     </row>
     <row r="49" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F49" s="5"/>
-      <c r="I49" s="5"/>
+      <c r="F49" s="9"/>
+      <c r="I49" s="9"/>
     </row>
     <row r="50" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F50" s="5"/>
-      <c r="I50" s="5"/>
+      <c r="F50" s="9"/>
+      <c r="I50" s="9"/>
     </row>
     <row r="51" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F51" s="5"/>
-      <c r="I51" s="5"/>
+      <c r="F51" s="9"/>
+      <c r="I51" s="9"/>
     </row>
     <row r="52" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F52" s="5"/>
-      <c r="I52" s="5"/>
+      <c r="F52" s="9"/>
+      <c r="I52" s="9"/>
     </row>
     <row r="53" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F53" s="5"/>
-      <c r="I53" s="5"/>
+      <c r="F53" s="9"/>
+      <c r="I53" s="9"/>
     </row>
     <row r="54" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F54" s="5"/>
-      <c r="I54" s="5"/>
+      <c r="F54" s="9"/>
+      <c r="I54" s="9"/>
     </row>
     <row r="55" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F55" s="5"/>
-      <c r="I55" s="5"/>
+      <c r="F55" s="9"/>
+      <c r="I55" s="9"/>
     </row>
     <row r="56" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F56" s="5"/>
-      <c r="I56" s="5"/>
+      <c r="F56" s="9"/>
+      <c r="I56" s="9"/>
     </row>
     <row r="57" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F57" s="5"/>
-      <c r="I57" s="5"/>
+      <c r="F57" s="9"/>
+      <c r="I57" s="9"/>
     </row>
     <row r="58" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F58" s="5"/>
-      <c r="I58" s="5"/>
+      <c r="F58" s="9"/>
+      <c r="I58" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K23" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}"/>
+  <autoFilter ref="A1:K23" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K23">
+      <sortCondition ref="B1:B23"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1641,465 +1647,470 @@
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="11" style="11"/>
+    <col min="1" max="1" width="7.7109375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="10" t="s">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="15">
-        <v>3</v>
-      </c>
-      <c r="E2" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F2" s="13">
-        <v>46052</v>
-      </c>
-      <c r="G2" s="15">
+      <c r="C2" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="3">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46052</v>
+      </c>
+      <c r="G2" s="3">
         <v>8179</v>
       </c>
-      <c r="H2" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I2" s="13">
-        <v>46048</v>
-      </c>
-      <c r="J2" s="16" t="s">
+      <c r="H2" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I2" s="4">
+        <v>46048</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46052</v>
+      </c>
+      <c r="G3" s="3">
+        <v>9209</v>
+      </c>
+      <c r="H3" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I3" s="4">
+        <v>46048</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46052</v>
+      </c>
+      <c r="G4" s="3">
+        <v>9258</v>
+      </c>
+      <c r="H4" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I4" s="4">
+        <v>46048</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46052</v>
+      </c>
+      <c r="G5" s="3">
+        <v>9345</v>
+      </c>
+      <c r="H5" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I5" s="4">
+        <v>46048</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46052</v>
+      </c>
+      <c r="G6" s="3">
+        <v>9315</v>
+      </c>
+      <c r="H6" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I6" s="4">
+        <v>46048</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46052</v>
+      </c>
+      <c r="G7" s="3">
+        <v>9137</v>
+      </c>
+      <c r="H7" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I7" s="4">
+        <v>46048</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F8" s="4">
+        <v>46052</v>
+      </c>
+      <c r="G8" s="3">
+        <v>9313</v>
+      </c>
+      <c r="H8" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I8" s="4">
+        <v>46048</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46052</v>
+      </c>
+      <c r="G9" s="3">
+        <v>9341</v>
+      </c>
+      <c r="H9" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I9" s="4">
+        <v>46048</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46052</v>
+      </c>
+      <c r="G10" s="3">
+        <v>9363</v>
+      </c>
+      <c r="H10" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I10" s="4">
+        <v>46048</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="15">
-        <v>3</v>
-      </c>
-      <c r="E3" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F3" s="13">
-        <v>46052</v>
-      </c>
-      <c r="G3" s="15">
+      <c r="C11" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46052</v>
+      </c>
+      <c r="G11" s="3">
         <v>8983</v>
       </c>
-      <c r="H3" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I3" s="13">
-        <v>46048</v>
-      </c>
-      <c r="J3" s="16" t="s">
+      <c r="H11" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I11" s="4">
+        <v>46048</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3</v>
+      </c>
+      <c r="E12" s="4">
+        <v>46048</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46052</v>
+      </c>
+      <c r="G12" s="3">
+        <v>9140</v>
+      </c>
+      <c r="H12" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I12" s="4">
+        <v>46048</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K12" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="15">
-        <v>3</v>
-      </c>
-      <c r="E4" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F4" s="13">
-        <v>46052</v>
-      </c>
-      <c r="G4" s="15">
-        <v>9137</v>
-      </c>
-      <c r="H4" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I4" s="13">
-        <v>46048</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="15">
-        <v>3</v>
-      </c>
-      <c r="E5" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F5" s="13">
-        <v>46052</v>
-      </c>
-      <c r="G5" s="15">
-        <v>9140</v>
-      </c>
-      <c r="H5" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I5" s="13">
-        <v>46048</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="15">
-        <v>3</v>
-      </c>
-      <c r="E6" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F6" s="13">
-        <v>46052</v>
-      </c>
-      <c r="G6" s="15">
-        <v>9209</v>
-      </c>
-      <c r="H6" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I6" s="13">
-        <v>46048</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="15">
-        <v>3</v>
-      </c>
-      <c r="E7" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F7" s="13">
-        <v>46052</v>
-      </c>
-      <c r="G7" s="15">
-        <v>9258</v>
-      </c>
-      <c r="H7" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I7" s="13">
-        <v>46048</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="15">
-        <v>3</v>
-      </c>
-      <c r="E8" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F8" s="13">
-        <v>46052</v>
-      </c>
-      <c r="G8" s="15">
-        <v>9313</v>
-      </c>
-      <c r="H8" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I8" s="13">
-        <v>46048</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="K8" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="15">
-        <v>3</v>
-      </c>
-      <c r="E9" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F9" s="13">
-        <v>46052</v>
-      </c>
-      <c r="G9" s="15">
-        <v>9315</v>
-      </c>
-      <c r="H9" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I9" s="13">
-        <v>46048</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="15">
-        <v>3</v>
-      </c>
-      <c r="E10" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F10" s="13">
-        <v>46052</v>
-      </c>
-      <c r="G10" s="15">
-        <v>9341</v>
-      </c>
-      <c r="H10" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I10" s="13">
-        <v>46048</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="15">
-        <v>3</v>
-      </c>
-      <c r="E11" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F11" s="13">
-        <v>46052</v>
-      </c>
-      <c r="G11" s="15">
-        <v>9345</v>
-      </c>
-      <c r="H11" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I11" s="13">
-        <v>46048</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="15">
-        <v>3</v>
-      </c>
-      <c r="E12" s="13">
-        <v>46048</v>
-      </c>
-      <c r="F12" s="13">
-        <v>46052</v>
-      </c>
-      <c r="G12" s="15">
-        <v>9363</v>
-      </c>
-      <c r="H12" s="14">
-        <v>46023</v>
-      </c>
-      <c r="I12" s="13">
-        <v>46048</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F13" s="5"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F14" s="5"/>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F15" s="5"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F16" s="5"/>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F17" s="5"/>
+      <c r="F17" s="9"/>
     </row>
     <row r="18" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F18" s="5"/>
+      <c r="F18" s="9"/>
     </row>
     <row r="19" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F19" s="5"/>
+      <c r="F19" s="9"/>
     </row>
     <row r="20" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F20" s="5"/>
+      <c r="F20" s="9"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{16A6A408-5BF6-4E16-8C71-EC6EB1F5A842}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K12">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
